--- a/lexicon backup.xlsx
+++ b/lexicon backup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jjohns/Desktop/Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6785CAF-C814-F74B-8F82-53D986515E10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0DEE322-671C-7A40-87AD-307CC8D7D315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="900" yWindow="660" windowWidth="28400" windowHeight="20520" xr2:uid="{94D6E9CA-AF84-3445-BCA6-352956A682AC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1478" uniqueCount="1177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="1219">
   <si>
     <t>oodham</t>
   </si>
@@ -3551,22 +3551,148 @@
     <t>audio/examples/haveyoueverseenamountainlion.mp3</t>
   </si>
   <si>
-    <t>dialect_id</t>
-  </si>
-  <si>
-    <t>features</t>
-  </si>
-  <si>
-    <t>Ak-Chin || Any</t>
-  </si>
-  <si>
-    <t>akchin</t>
-  </si>
-  <si>
-    <t>Tohono O’odham || Any</t>
-  </si>
-  <si>
-    <t>tohono</t>
+    <t>Ak-Chin</t>
+  </si>
+  <si>
+    <t>Tohono O’odham</t>
+  </si>
+  <si>
+    <t>Tohono O'odham || Any</t>
+  </si>
+  <si>
+    <t>lai</t>
+  </si>
+  <si>
+    <t>king</t>
+  </si>
+  <si>
+    <t>[ɽɑi]</t>
+  </si>
+  <si>
+    <t>lalai</t>
+  </si>
+  <si>
+    <t>[ˈɽɑ.ɽɑi]</t>
+  </si>
+  <si>
+    <t>kings</t>
+  </si>
+  <si>
+    <t>kovnal</t>
+  </si>
+  <si>
+    <t>council member</t>
+  </si>
+  <si>
+    <t>[ˈkɔv.nɑɽ]</t>
+  </si>
+  <si>
+    <t>kokovnal</t>
+  </si>
+  <si>
+    <t>[ˈkɔ.kɔv.nɑɽ]</t>
+  </si>
+  <si>
+    <t>council members</t>
+  </si>
+  <si>
+    <t>pikcul</t>
+  </si>
+  <si>
+    <t>picture</t>
+  </si>
+  <si>
+    <t>[ˈpik.cuɽ]</t>
+  </si>
+  <si>
+    <t>pipikcul</t>
+  </si>
+  <si>
+    <t>[ˈpi.pik.cuɽ]</t>
+  </si>
+  <si>
+    <t>nouns</t>
+  </si>
+  <si>
+    <t>vepgi-kahon</t>
+  </si>
+  <si>
+    <t>TV</t>
+  </si>
+  <si>
+    <t>0 - 1</t>
+  </si>
+  <si>
+    <t>[ˈvɯp.gi ˈkɑ.hɔn]</t>
+  </si>
+  <si>
+    <t>vepgi-kakhon</t>
+  </si>
+  <si>
+    <t>[ˈvɯp.gi ˈkɑk.hɔn]</t>
+  </si>
+  <si>
+    <t>TVs</t>
+  </si>
+  <si>
+    <t>pasahi:lo</t>
+  </si>
+  <si>
+    <t>train (that people ride on)</t>
+  </si>
+  <si>
+    <t>[ˈpɑ.sɑ.hiː.ɽɔ]</t>
+  </si>
+  <si>
+    <t>papsahi:lo</t>
+  </si>
+  <si>
+    <t>[ˈpɑp.sɑ.hiː.ɽɔ]</t>
+  </si>
+  <si>
+    <t>trains (that people ride on)</t>
+  </si>
+  <si>
+    <t>vainom kalit</t>
+  </si>
+  <si>
+    <t>train (for cargo)</t>
+  </si>
+  <si>
+    <t>2 - 1</t>
+  </si>
+  <si>
+    <t>[ˈvɑi.nom ˈkɑ.ɽit̪]</t>
+  </si>
+  <si>
+    <t>vapainom kaklit</t>
+  </si>
+  <si>
+    <t>[ˈvɑ.pɑi.nom ˈkɑk.ɽit̪]</t>
+  </si>
+  <si>
+    <t>trains (for cargo)</t>
+  </si>
+  <si>
+    <t>vainom ki:</t>
+  </si>
+  <si>
+    <t>trailer home</t>
+  </si>
+  <si>
+    <t>2 - 8</t>
+  </si>
+  <si>
+    <t>[ˈvɑi.nom ˈkiː]</t>
+  </si>
+  <si>
+    <t>vapainom ki:kĭ</t>
+  </si>
+  <si>
+    <t>[ˈvɑ.pɑi.nom ˈkiː.kĭ]</t>
+  </si>
+  <si>
+    <t>trailer homes</t>
   </si>
 </sst>
 </file>
@@ -3609,7 +3735,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3619,6 +3745,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3953,7 +4085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5C70B7F-39B1-CF49-AFC9-B05A2423C135}">
-  <dimension ref="A1:Q139"/>
+  <dimension ref="A1:O146"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -3972,7 +4104,7 @@
     <col min="14" max="14" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3982,7 +4114,7 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
@@ -4000,29 +4132,23 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>1171</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" t="s">
-        <v>1172</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="85" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -4032,7 +4158,7 @@
       <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="5">
         <v>7</v>
       </c>
       <c r="E2" t="s">
@@ -4050,21 +4176,20 @@
       <c r="I2" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
       <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" t="s">
         <v>23</v>
       </c>
-      <c r="O2" t="s">
+      <c r="N2" t="s">
         <v>1073</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="187" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -4074,7 +4199,7 @@
       <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="5">
         <v>7</v>
       </c>
       <c r="E3" t="s">
@@ -4090,28 +4215,25 @@
         <v>29</v>
       </c>
       <c r="I3" t="s">
-        <v>1173</v>
-      </c>
-      <c r="J3" t="s">
-        <v>1174</v>
-      </c>
-      <c r="K3" s="1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="K3" t="s">
+        <v>31</v>
+      </c>
       <c r="L3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M3" t="s">
-        <v>32</v>
+        <v>1034</v>
       </c>
       <c r="N3" t="s">
-        <v>1034</v>
-      </c>
-      <c r="O3" t="s">
         <v>1074</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="85" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -4121,7 +4243,7 @@
       <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="5">
         <v>7</v>
       </c>
       <c r="E4" t="s">
@@ -4139,21 +4261,20 @@
       <c r="I4" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>1033</v>
       </c>
+      <c r="K4" t="s">
+        <v>38</v>
+      </c>
       <c r="L4" t="s">
-        <v>38</v>
-      </c>
-      <c r="M4" t="s">
         <v>39</v>
       </c>
-      <c r="O4" t="s">
+      <c r="N4" t="s">
         <v>1075</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="119" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="187" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -4163,7 +4284,7 @@
       <c r="C5" t="s">
         <v>16</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
@@ -4181,21 +4302,20 @@
       <c r="I5" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="K5" t="s">
+        <v>47</v>
+      </c>
       <c r="L5" t="s">
-        <v>47</v>
-      </c>
-      <c r="M5" t="s">
         <v>48</v>
       </c>
-      <c r="O5" t="s">
+      <c r="N5" t="s">
         <v>1076</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -4205,7 +4325,7 @@
       <c r="C6" t="s">
         <v>16</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="5">
         <v>1</v>
       </c>
       <c r="E6" t="s">
@@ -4223,21 +4343,20 @@
       <c r="I6" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="K6" t="s">
+        <v>56</v>
+      </c>
       <c r="L6" t="s">
-        <v>56</v>
-      </c>
-      <c r="M6" t="s">
         <v>57</v>
       </c>
-      <c r="O6" t="s">
+      <c r="N6" t="s">
         <v>1077</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="153" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -4247,7 +4366,7 @@
       <c r="C7" t="s">
         <v>16</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="5">
         <v>7</v>
       </c>
       <c r="E7" t="s">
@@ -4265,21 +4384,20 @@
       <c r="I7" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="K7" t="s">
+        <v>65</v>
+      </c>
       <c r="L7" t="s">
-        <v>65</v>
-      </c>
-      <c r="M7" t="s">
         <v>66</v>
       </c>
-      <c r="O7" t="s">
+      <c r="N7" t="s">
         <v>1078</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="68" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>67</v>
       </c>
@@ -4289,7 +4407,7 @@
       <c r="C8" t="s">
         <v>16</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="5">
         <v>7</v>
       </c>
       <c r="E8" t="s">
@@ -4307,21 +4425,20 @@
       <c r="I8" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="1" t="s">
+      <c r="J8" s="1" t="s">
         <v>73</v>
       </c>
+      <c r="K8" t="s">
+        <v>74</v>
+      </c>
       <c r="L8" t="s">
-        <v>74</v>
-      </c>
-      <c r="M8" t="s">
         <v>75</v>
       </c>
-      <c r="O8" t="s">
+      <c r="N8" t="s">
         <v>1079</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>76</v>
       </c>
@@ -4331,7 +4448,7 @@
       <c r="C9" t="s">
         <v>16</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="5">
         <v>4</v>
       </c>
       <c r="E9" t="s">
@@ -4347,22 +4464,22 @@
         <v>81</v>
       </c>
       <c r="I9" t="s">
-        <v>1173</v>
-      </c>
-      <c r="K9" s="1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>82</v>
       </c>
+      <c r="K9" t="s">
+        <v>83</v>
+      </c>
       <c r="L9" t="s">
-        <v>83</v>
-      </c>
-      <c r="M9" t="s">
         <v>84</v>
       </c>
-      <c r="O9" t="s">
+      <c r="N9" t="s">
         <v>1080</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>85</v>
       </c>
@@ -4372,7 +4489,7 @@
       <c r="C10" t="s">
         <v>16</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="5">
         <v>3</v>
       </c>
       <c r="E10" t="s">
@@ -4388,25 +4505,22 @@
         <v>81</v>
       </c>
       <c r="I10" t="s">
-        <v>1175</v>
-      </c>
-      <c r="J10" t="s">
-        <v>1176</v>
-      </c>
-      <c r="K10" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>82</v>
       </c>
+      <c r="K10" t="s">
+        <v>86</v>
+      </c>
       <c r="L10" t="s">
-        <v>86</v>
-      </c>
-      <c r="M10" t="s">
         <v>87</v>
       </c>
-      <c r="O10" t="s">
+      <c r="N10" t="s">
         <v>1080</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>88</v>
       </c>
@@ -4416,7 +4530,7 @@
       <c r="C11" t="s">
         <v>16</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="5">
         <v>2</v>
       </c>
       <c r="E11" t="s">
@@ -4434,21 +4548,20 @@
       <c r="I11" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>93</v>
       </c>
+      <c r="K11" t="s">
+        <v>94</v>
+      </c>
       <c r="L11" t="s">
-        <v>94</v>
-      </c>
-      <c r="M11" t="s">
         <v>95</v>
       </c>
-      <c r="O11" t="s">
+      <c r="N11" t="s">
         <v>1081</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>96</v>
       </c>
@@ -4458,7 +4571,7 @@
       <c r="C12" t="s">
         <v>16</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="5">
         <v>2</v>
       </c>
       <c r="E12" t="s">
@@ -4476,21 +4589,20 @@
       <c r="I12" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>102</v>
       </c>
+      <c r="K12" t="s">
+        <v>103</v>
+      </c>
       <c r="L12" t="s">
-        <v>103</v>
-      </c>
-      <c r="M12" t="s">
         <v>104</v>
       </c>
-      <c r="O12" t="s">
+      <c r="N12" t="s">
         <v>1082</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ht="170" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>105</v>
       </c>
@@ -4500,7 +4612,7 @@
       <c r="C13" t="s">
         <v>16</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="5">
         <v>2</v>
       </c>
       <c r="E13" t="s">
@@ -4518,21 +4630,20 @@
       <c r="I13" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>111</v>
       </c>
+      <c r="K13" t="s">
+        <v>112</v>
+      </c>
       <c r="L13" t="s">
-        <v>112</v>
-      </c>
-      <c r="M13" t="s">
         <v>113</v>
       </c>
-      <c r="O13" t="s">
+      <c r="N13" t="s">
         <v>1083</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="68" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>114</v>
       </c>
@@ -4542,7 +4653,7 @@
       <c r="C14" t="s">
         <v>16</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="5">
         <v>7</v>
       </c>
       <c r="E14" t="s">
@@ -4560,21 +4671,20 @@
       <c r="I14" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>120</v>
       </c>
+      <c r="K14" t="s">
+        <v>121</v>
+      </c>
       <c r="L14" t="s">
-        <v>121</v>
-      </c>
-      <c r="M14" t="s">
         <v>122</v>
       </c>
-      <c r="O14" t="s">
+      <c r="N14" t="s">
         <v>1084</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="51" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>123</v>
       </c>
@@ -4584,7 +4694,7 @@
       <c r="C15" t="s">
         <v>16</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="5">
         <v>7</v>
       </c>
       <c r="E15" t="s">
@@ -4602,21 +4712,20 @@
       <c r="I15" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>129</v>
       </c>
+      <c r="K15" t="s">
+        <v>130</v>
+      </c>
       <c r="L15" t="s">
-        <v>130</v>
-      </c>
-      <c r="M15" t="s">
         <v>131</v>
       </c>
-      <c r="O15" t="s">
+      <c r="N15" t="s">
         <v>1085</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="51" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>132</v>
       </c>
@@ -4626,7 +4735,7 @@
       <c r="C16" t="s">
         <v>16</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="5">
         <v>7</v>
       </c>
       <c r="E16" t="s">
@@ -4644,21 +4753,20 @@
       <c r="I16" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="1" t="s">
+      <c r="J16" s="1" t="s">
         <v>138</v>
       </c>
+      <c r="K16" t="s">
+        <v>139</v>
+      </c>
       <c r="L16" t="s">
-        <v>139</v>
-      </c>
-      <c r="M16" t="s">
         <v>140</v>
       </c>
-      <c r="O16" t="s">
+      <c r="N16" t="s">
         <v>1086</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="68" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>141</v>
       </c>
@@ -4668,7 +4776,7 @@
       <c r="C17" t="s">
         <v>16</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="5">
         <v>2</v>
       </c>
       <c r="E17" t="s">
@@ -4686,21 +4794,20 @@
       <c r="I17" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>147</v>
       </c>
+      <c r="K17" t="s">
+        <v>148</v>
+      </c>
       <c r="L17" t="s">
-        <v>148</v>
-      </c>
-      <c r="M17" t="s">
         <v>149</v>
       </c>
-      <c r="O17" t="s">
+      <c r="N17" t="s">
         <v>1087</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>150</v>
       </c>
@@ -4710,24 +4817,24 @@
       <c r="C18" t="s">
         <v>16</v>
       </c>
+      <c r="D18" s="5"/>
       <c r="E18" t="s">
         <v>152</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="1" t="s">
+      <c r="J18" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="L18" t="s">
+      <c r="K18" t="s">
         <v>154</v>
       </c>
-      <c r="O18" t="s">
+      <c r="N18" t="s">
         <v>1088</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="136" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" ht="238" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>155</v>
       </c>
@@ -4737,7 +4844,7 @@
       <c r="C19" t="s">
         <v>16</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="5">
         <v>1</v>
       </c>
       <c r="E19" t="s">
@@ -4755,21 +4862,20 @@
       <c r="I19" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="1" t="s">
+      <c r="J19" s="1" t="s">
         <v>161</v>
       </c>
+      <c r="K19" t="s">
+        <v>162</v>
+      </c>
       <c r="L19" t="s">
-        <v>162</v>
-      </c>
-      <c r="M19" t="s">
         <v>163</v>
       </c>
-      <c r="O19" t="s">
+      <c r="N19" t="s">
         <v>1089</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>164</v>
       </c>
@@ -4779,26 +4885,27 @@
       <c r="C20" t="s">
         <v>16</v>
       </c>
+      <c r="D20" s="5"/>
       <c r="E20" t="s">
         <v>166</v>
       </c>
       <c r="I20" t="s">
-        <v>1173</v>
-      </c>
-      <c r="K20" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="L20" t="s">
+      <c r="K20" t="s">
         <v>168</v>
       </c>
+      <c r="M20" t="s">
+        <v>169</v>
+      </c>
       <c r="N20" t="s">
-        <v>169</v>
-      </c>
-      <c r="O20" t="s">
         <v>1090</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>170</v>
       </c>
@@ -4808,7 +4915,7 @@
       <c r="C21" t="s">
         <v>16</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="5">
         <v>2</v>
       </c>
       <c r="E21" t="s">
@@ -4826,21 +4933,20 @@
       <c r="I21" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="1" t="s">
+      <c r="J21" s="1" t="s">
         <v>176</v>
       </c>
+      <c r="K21" t="s">
+        <v>177</v>
+      </c>
       <c r="L21" t="s">
-        <v>177</v>
-      </c>
-      <c r="M21" t="s">
         <v>178</v>
       </c>
-      <c r="O21" t="s">
+      <c r="N21" t="s">
         <v>1091</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="85" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>179</v>
       </c>
@@ -4850,7 +4956,7 @@
       <c r="C22" t="s">
         <v>16</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="5">
         <v>2</v>
       </c>
       <c r="E22" t="s">
@@ -4868,21 +4974,20 @@
       <c r="I22" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>185</v>
       </c>
+      <c r="K22" t="s">
+        <v>186</v>
+      </c>
       <c r="L22" t="s">
-        <v>186</v>
-      </c>
-      <c r="M22" t="s">
         <v>187</v>
       </c>
-      <c r="O22" t="s">
+      <c r="N22" t="s">
         <v>1092</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>188</v>
       </c>
@@ -4892,7 +4997,7 @@
       <c r="C23" t="s">
         <v>16</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="5">
         <v>1</v>
       </c>
       <c r="E23" t="s">
@@ -4910,21 +5015,20 @@
       <c r="I23" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="1" t="s">
+      <c r="J23" s="1" t="s">
         <v>194</v>
       </c>
+      <c r="K23" t="s">
+        <v>195</v>
+      </c>
       <c r="L23" t="s">
-        <v>195</v>
-      </c>
-      <c r="M23" t="s">
         <v>196</v>
       </c>
-      <c r="O23" t="s">
+      <c r="N23" t="s">
         <v>1093</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>197</v>
       </c>
@@ -4934,7 +5038,7 @@
       <c r="C24" t="s">
         <v>16</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="5">
         <v>7</v>
       </c>
       <c r="E24" t="s">
@@ -4952,21 +5056,20 @@
       <c r="I24" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="1" t="s">
+      <c r="J24" s="1" t="s">
         <v>203</v>
       </c>
+      <c r="K24" t="s">
+        <v>204</v>
+      </c>
       <c r="L24" t="s">
-        <v>204</v>
-      </c>
-      <c r="M24" t="s">
         <v>205</v>
       </c>
-      <c r="O24" t="s">
+      <c r="N24" t="s">
         <v>1094</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>206</v>
       </c>
@@ -4976,7 +5079,7 @@
       <c r="C25" t="s">
         <v>16</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="5">
         <v>2</v>
       </c>
       <c r="E25" t="s">
@@ -4994,21 +5097,20 @@
       <c r="I25" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="1" t="s">
+      <c r="J25" s="1" t="s">
         <v>212</v>
       </c>
+      <c r="K25" t="s">
+        <v>213</v>
+      </c>
       <c r="L25" t="s">
-        <v>213</v>
-      </c>
-      <c r="M25" t="s">
         <v>214</v>
       </c>
-      <c r="O25" t="s">
+      <c r="N25" t="s">
         <v>1095</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>215</v>
       </c>
@@ -5018,27 +5120,27 @@
       <c r="C26" t="s">
         <v>217</v>
       </c>
+      <c r="D26" s="5"/>
       <c r="E26" t="s">
         <v>218</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="1" t="s">
+      <c r="J26" s="1" t="s">
         <v>219</v>
       </c>
+      <c r="K26" t="s">
+        <v>220</v>
+      </c>
       <c r="L26" t="s">
-        <v>220</v>
-      </c>
-      <c r="M26" t="s">
         <v>221</v>
       </c>
-      <c r="O26" t="s">
+      <c r="N26" t="s">
         <v>1096</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="68" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>222</v>
       </c>
@@ -5048,7 +5150,7 @@
       <c r="C27" t="s">
         <v>16</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="5">
         <v>2</v>
       </c>
       <c r="E27" t="s">
@@ -5066,21 +5168,20 @@
       <c r="I27" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="1" t="s">
+      <c r="J27" s="1" t="s">
         <v>228</v>
       </c>
+      <c r="K27" t="s">
+        <v>229</v>
+      </c>
       <c r="L27" t="s">
-        <v>229</v>
-      </c>
-      <c r="M27" t="s">
         <v>230</v>
       </c>
-      <c r="O27" t="s">
+      <c r="N27" t="s">
         <v>1097</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="102" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" ht="170" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>231</v>
       </c>
@@ -5090,7 +5191,7 @@
       <c r="C28" t="s">
         <v>16</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="5">
         <v>7</v>
       </c>
       <c r="E28" t="s">
@@ -5108,21 +5209,20 @@
       <c r="I28" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="1" t="s">
+      <c r="J28" s="1" t="s">
         <v>1057</v>
       </c>
+      <c r="K28" t="s">
+        <v>237</v>
+      </c>
       <c r="L28" t="s">
-        <v>237</v>
-      </c>
-      <c r="M28" t="s">
         <v>238</v>
       </c>
-      <c r="O28" t="s">
+      <c r="N28" t="s">
         <v>1098</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="85" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>239</v>
       </c>
@@ -5132,7 +5232,7 @@
       <c r="C29" t="s">
         <v>16</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="5">
         <v>7</v>
       </c>
       <c r="E29" t="s">
@@ -5150,21 +5250,20 @@
       <c r="I29" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="1" t="s">
+      <c r="J29" s="1" t="s">
         <v>245</v>
       </c>
+      <c r="K29" t="s">
+        <v>246</v>
+      </c>
       <c r="L29" t="s">
-        <v>246</v>
-      </c>
-      <c r="M29" t="s">
         <v>247</v>
       </c>
-      <c r="O29" t="s">
+      <c r="N29" t="s">
         <v>1099</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="85" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>248</v>
       </c>
@@ -5174,7 +5273,7 @@
       <c r="C30" t="s">
         <v>16</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="5">
         <v>2</v>
       </c>
       <c r="E30" t="s">
@@ -5192,21 +5291,20 @@
       <c r="I30" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="1" t="s">
+      <c r="J30" s="1" t="s">
         <v>254</v>
       </c>
+      <c r="K30" t="s">
+        <v>255</v>
+      </c>
       <c r="L30" t="s">
-        <v>255</v>
-      </c>
-      <c r="M30" t="s">
         <v>256</v>
       </c>
-      <c r="O30" t="s">
+      <c r="N30" t="s">
         <v>1100</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="68" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>257</v>
       </c>
@@ -5216,7 +5314,7 @@
       <c r="C31" t="s">
         <v>16</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="5">
         <v>1</v>
       </c>
       <c r="E31" t="s">
@@ -5234,21 +5332,20 @@
       <c r="I31" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J31" s="3"/>
-      <c r="K31" s="1" t="s">
+      <c r="J31" s="1" t="s">
         <v>1058</v>
       </c>
+      <c r="K31" t="s">
+        <v>263</v>
+      </c>
       <c r="L31" t="s">
-        <v>263</v>
-      </c>
-      <c r="M31" t="s">
         <v>264</v>
       </c>
-      <c r="O31" t="s">
+      <c r="N31" t="s">
         <v>1101</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>265</v>
       </c>
@@ -5258,7 +5355,7 @@
       <c r="C32" t="s">
         <v>16</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="5">
         <v>1</v>
       </c>
       <c r="E32" t="s">
@@ -5276,21 +5373,20 @@
       <c r="I32" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J32" s="3"/>
-      <c r="K32" s="1" t="s">
+      <c r="J32" s="1" t="s">
         <v>271</v>
       </c>
+      <c r="K32" t="s">
+        <v>272</v>
+      </c>
       <c r="L32" t="s">
-        <v>272</v>
-      </c>
-      <c r="M32" t="s">
         <v>273</v>
       </c>
-      <c r="O32" t="s">
+      <c r="N32" t="s">
         <v>1102</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>274</v>
       </c>
@@ -5300,7 +5396,7 @@
       <c r="C33" t="s">
         <v>16</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="5">
         <v>1</v>
       </c>
       <c r="E33" t="s">
@@ -5318,21 +5414,20 @@
       <c r="I33" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J33" s="3"/>
-      <c r="K33" s="1" t="s">
+      <c r="J33" s="1" t="s">
         <v>280</v>
       </c>
+      <c r="K33" t="s">
+        <v>288</v>
+      </c>
       <c r="L33" t="s">
-        <v>288</v>
-      </c>
-      <c r="M33" t="s">
         <v>289</v>
       </c>
-      <c r="O33" t="s">
+      <c r="N33" t="s">
         <v>1103</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>283</v>
       </c>
@@ -5342,7 +5437,7 @@
       <c r="C34" t="s">
         <v>16</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="5">
         <v>1</v>
       </c>
       <c r="E34" t="s">
@@ -5360,21 +5455,20 @@
       <c r="I34" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J34" s="3"/>
-      <c r="K34" s="1" t="s">
+      <c r="J34" s="1" t="s">
         <v>287</v>
       </c>
+      <c r="K34" t="s">
+        <v>281</v>
+      </c>
       <c r="L34" t="s">
-        <v>281</v>
-      </c>
-      <c r="M34" t="s">
         <v>282</v>
       </c>
-      <c r="O34" t="s">
+      <c r="N34" t="s">
         <v>1104</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>290</v>
       </c>
@@ -5384,7 +5478,7 @@
       <c r="C35" t="s">
         <v>16</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="5">
         <v>2</v>
       </c>
       <c r="E35" t="s">
@@ -5402,21 +5496,20 @@
       <c r="I35" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J35" s="3"/>
-      <c r="K35" s="1" t="s">
+      <c r="J35" s="1" t="s">
         <v>294</v>
       </c>
+      <c r="K35" t="s">
+        <v>295</v>
+      </c>
       <c r="L35" t="s">
-        <v>295</v>
-      </c>
-      <c r="M35" t="s">
         <v>296</v>
       </c>
-      <c r="O35" t="s">
+      <c r="N35" t="s">
         <v>1105</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>297</v>
       </c>
@@ -5426,7 +5519,7 @@
       <c r="C36" t="s">
         <v>16</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="5">
         <v>4</v>
       </c>
       <c r="E36" t="s">
@@ -5444,21 +5537,20 @@
       <c r="I36" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J36" s="3"/>
-      <c r="K36" s="1" t="s">
+      <c r="J36" s="1" t="s">
         <v>303</v>
       </c>
+      <c r="K36" t="s">
+        <v>304</v>
+      </c>
       <c r="L36" t="s">
-        <v>304</v>
-      </c>
-      <c r="M36" t="s">
         <v>305</v>
       </c>
-      <c r="O36" t="s">
+      <c r="N36" t="s">
         <v>1106</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>306</v>
       </c>
@@ -5468,7 +5560,7 @@
       <c r="C37" t="s">
         <v>16</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="5">
         <v>2</v>
       </c>
       <c r="E37" t="s">
@@ -5486,21 +5578,20 @@
       <c r="I37" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J37" s="3"/>
-      <c r="K37" s="1" t="s">
+      <c r="J37" s="1" t="s">
         <v>312</v>
       </c>
+      <c r="K37" t="s">
+        <v>313</v>
+      </c>
       <c r="L37" t="s">
-        <v>313</v>
-      </c>
-      <c r="M37" t="s">
         <v>314</v>
       </c>
-      <c r="O37" t="s">
+      <c r="N37" t="s">
         <v>1107</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="68" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>315</v>
       </c>
@@ -5510,7 +5601,7 @@
       <c r="C38" t="s">
         <v>16</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="5">
         <v>7</v>
       </c>
       <c r="E38" t="s">
@@ -5528,21 +5619,20 @@
       <c r="I38" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J38" s="3"/>
-      <c r="K38" s="1" t="s">
+      <c r="J38" s="1" t="s">
         <v>1059</v>
       </c>
+      <c r="K38" t="s">
+        <v>321</v>
+      </c>
       <c r="L38" t="s">
-        <v>321</v>
-      </c>
-      <c r="M38" t="s">
         <v>322</v>
       </c>
-      <c r="O38" t="s">
+      <c r="N38" t="s">
         <v>1108</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>323</v>
       </c>
@@ -5552,7 +5642,7 @@
       <c r="C39" t="s">
         <v>16</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="5">
         <v>7</v>
       </c>
       <c r="E39" t="s">
@@ -5570,21 +5660,20 @@
       <c r="I39" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J39" s="3"/>
-      <c r="K39" s="1" t="s">
+      <c r="J39" s="1" t="s">
         <v>329</v>
       </c>
+      <c r="K39" t="s">
+        <v>330</v>
+      </c>
       <c r="L39" t="s">
-        <v>330</v>
-      </c>
-      <c r="M39" t="s">
         <v>331</v>
       </c>
-      <c r="O39" t="s">
+      <c r="N39" t="s">
         <v>1109</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="85" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" ht="119" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>332</v>
       </c>
@@ -5594,7 +5683,7 @@
       <c r="C40" t="s">
         <v>16</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="5">
         <v>3</v>
       </c>
       <c r="E40" t="s">
@@ -5612,21 +5701,20 @@
       <c r="I40" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J40" s="3"/>
-      <c r="K40" s="1" t="s">
+      <c r="J40" s="1" t="s">
         <v>338</v>
       </c>
+      <c r="K40" t="s">
+        <v>339</v>
+      </c>
       <c r="L40" t="s">
-        <v>339</v>
-      </c>
-      <c r="M40" t="s">
         <v>340</v>
       </c>
-      <c r="O40" t="s">
+      <c r="N40" t="s">
         <v>1110</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="68" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>341</v>
       </c>
@@ -5636,7 +5724,7 @@
       <c r="C41" t="s">
         <v>16</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="5">
         <v>3</v>
       </c>
       <c r="E41" t="s">
@@ -5654,21 +5742,20 @@
       <c r="I41" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J41" s="3"/>
-      <c r="K41" s="1" t="s">
+      <c r="J41" s="1" t="s">
         <v>345</v>
       </c>
+      <c r="K41" t="s">
+        <v>346</v>
+      </c>
       <c r="L41" t="s">
-        <v>346</v>
-      </c>
-      <c r="M41" t="s">
         <v>347</v>
       </c>
-      <c r="O41" t="s">
+      <c r="N41" t="s">
         <v>1111</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="68" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>348</v>
       </c>
@@ -5678,7 +5765,7 @@
       <c r="C42" t="s">
         <v>16</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="5">
         <v>2</v>
       </c>
       <c r="E42" t="s">
@@ -5696,21 +5783,20 @@
       <c r="I42" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J42" s="3"/>
-      <c r="K42" s="1" t="s">
+      <c r="J42" s="1" t="s">
         <v>354</v>
       </c>
+      <c r="K42" t="s">
+        <v>355</v>
+      </c>
       <c r="L42" t="s">
-        <v>355</v>
-      </c>
-      <c r="M42" t="s">
         <v>356</v>
       </c>
-      <c r="O42" t="s">
+      <c r="N42" t="s">
         <v>1112</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>357</v>
       </c>
@@ -5720,7 +5806,7 @@
       <c r="C43" t="s">
         <v>16</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="5">
         <v>2</v>
       </c>
       <c r="E43" t="s">
@@ -5738,21 +5824,20 @@
       <c r="I43" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J43" s="3"/>
-      <c r="K43" s="1" t="s">
+      <c r="J43" s="1" t="s">
         <v>363</v>
       </c>
+      <c r="K43" t="s">
+        <v>364</v>
+      </c>
       <c r="L43" t="s">
-        <v>364</v>
-      </c>
-      <c r="M43" t="s">
         <v>365</v>
       </c>
-      <c r="O43" t="s">
+      <c r="N43" t="s">
         <v>1113</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="68" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>366</v>
       </c>
@@ -5762,7 +5847,7 @@
       <c r="C44" t="s">
         <v>16</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="5">
         <v>1</v>
       </c>
       <c r="E44" t="s">
@@ -5780,21 +5865,20 @@
       <c r="I44" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J44" s="3"/>
-      <c r="K44" s="1" t="s">
+      <c r="J44" s="1" t="s">
         <v>372</v>
+      </c>
+      <c r="K44" t="s">
+        <v>373</v>
       </c>
       <c r="L44" t="s">
         <v>373</v>
       </c>
-      <c r="M44" t="s">
-        <v>373</v>
-      </c>
-      <c r="O44" t="s">
+      <c r="N44" t="s">
         <v>1114</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>374</v>
       </c>
@@ -5804,7 +5888,7 @@
       <c r="C45" t="s">
         <v>16</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="5">
         <v>2</v>
       </c>
       <c r="E45" t="s">
@@ -5822,21 +5906,20 @@
       <c r="I45" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J45" s="3"/>
-      <c r="K45" s="1" t="s">
+      <c r="J45" s="1" t="s">
         <v>380</v>
       </c>
+      <c r="K45" t="s">
+        <v>381</v>
+      </c>
       <c r="L45" t="s">
-        <v>381</v>
-      </c>
-      <c r="M45" t="s">
         <v>382</v>
       </c>
-      <c r="O45" t="s">
+      <c r="N45" t="s">
         <v>1115</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>383</v>
       </c>
@@ -5846,7 +5929,7 @@
       <c r="C46" t="s">
         <v>16</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="5">
         <v>1</v>
       </c>
       <c r="E46" t="s">
@@ -5864,21 +5947,20 @@
       <c r="I46" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J46" s="3"/>
-      <c r="K46" s="1" t="s">
+      <c r="J46" s="1" t="s">
         <v>389</v>
       </c>
+      <c r="K46" t="s">
+        <v>390</v>
+      </c>
       <c r="L46" t="s">
-        <v>390</v>
-      </c>
-      <c r="M46" t="s">
         <v>391</v>
       </c>
-      <c r="O46" t="s">
+      <c r="N46" t="s">
         <v>1116</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>392</v>
       </c>
@@ -5888,7 +5970,7 @@
       <c r="C47" t="s">
         <v>16</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="5">
         <v>1</v>
       </c>
       <c r="E47" t="s">
@@ -5906,21 +5988,20 @@
       <c r="I47" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J47" s="3"/>
-      <c r="K47" s="1" t="s">
+      <c r="J47" s="1" t="s">
         <v>398</v>
       </c>
+      <c r="K47" t="s">
+        <v>399</v>
+      </c>
       <c r="L47" t="s">
-        <v>399</v>
-      </c>
-      <c r="M47" t="s">
         <v>400</v>
       </c>
-      <c r="O47" t="s">
+      <c r="N47" t="s">
         <v>1117</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>401</v>
       </c>
@@ -5930,7 +6011,7 @@
       <c r="C48" t="s">
         <v>16</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="5">
         <v>2</v>
       </c>
       <c r="E48" t="s">
@@ -5948,21 +6029,20 @@
       <c r="I48" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J48" s="3"/>
-      <c r="K48" s="1" t="s">
+      <c r="J48" s="1" t="s">
         <v>407</v>
       </c>
+      <c r="K48" t="s">
+        <v>408</v>
+      </c>
       <c r="L48" t="s">
-        <v>408</v>
-      </c>
-      <c r="M48" t="s">
         <v>409</v>
       </c>
-      <c r="O48" t="s">
+      <c r="N48" t="s">
         <v>1118</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>410</v>
       </c>
@@ -5972,7 +6052,7 @@
       <c r="C49" t="s">
         <v>16</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="5">
         <v>7</v>
       </c>
       <c r="E49" t="s">
@@ -5990,21 +6070,20 @@
       <c r="I49" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J49" s="3"/>
-      <c r="K49" s="1" t="s">
+      <c r="J49" s="1" t="s">
         <v>416</v>
       </c>
+      <c r="K49" t="s">
+        <v>417</v>
+      </c>
       <c r="L49" t="s">
-        <v>417</v>
-      </c>
-      <c r="M49" t="s">
         <v>418</v>
       </c>
-      <c r="O49" t="s">
+      <c r="N49" t="s">
         <v>1119</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>419</v>
       </c>
@@ -6014,7 +6093,7 @@
       <c r="C50" t="s">
         <v>16</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="5">
         <v>4</v>
       </c>
       <c r="E50" t="s">
@@ -6032,21 +6111,20 @@
       <c r="I50" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J50" s="3"/>
-      <c r="K50" s="1" t="s">
+      <c r="J50" s="1" t="s">
         <v>425</v>
       </c>
+      <c r="K50" t="s">
+        <v>426</v>
+      </c>
       <c r="L50" t="s">
-        <v>426</v>
-      </c>
-      <c r="M50" t="s">
         <v>427</v>
       </c>
-      <c r="O50" t="s">
+      <c r="N50" t="s">
         <v>1120</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>428</v>
       </c>
@@ -6056,7 +6134,7 @@
       <c r="C51" t="s">
         <v>16</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="5">
         <v>2</v>
       </c>
       <c r="E51" t="s">
@@ -6074,21 +6152,20 @@
       <c r="I51" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J51" s="3"/>
-      <c r="K51" s="1" t="s">
+      <c r="J51" s="1" t="s">
         <v>434</v>
       </c>
+      <c r="K51" t="s">
+        <v>435</v>
+      </c>
       <c r="L51" t="s">
-        <v>435</v>
-      </c>
-      <c r="M51" t="s">
         <v>436</v>
       </c>
-      <c r="O51" t="s">
+      <c r="N51" t="s">
         <v>1121</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>437</v>
       </c>
@@ -6098,7 +6175,7 @@
       <c r="C52" t="s">
         <v>16</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="5">
         <v>2</v>
       </c>
       <c r="E52" t="s">
@@ -6116,21 +6193,20 @@
       <c r="I52" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J52" s="3"/>
-      <c r="K52" s="1" t="s">
+      <c r="J52" s="1" t="s">
         <v>443</v>
       </c>
+      <c r="K52" t="s">
+        <v>444</v>
+      </c>
       <c r="L52" t="s">
-        <v>444</v>
-      </c>
-      <c r="M52" t="s">
         <v>445</v>
       </c>
-      <c r="O52" t="s">
+      <c r="N52" t="s">
         <v>1122</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>446</v>
       </c>
@@ -6140,7 +6216,7 @@
       <c r="C53" t="s">
         <v>16</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="5">
         <v>4</v>
       </c>
       <c r="E53" t="s">
@@ -6158,21 +6234,20 @@
       <c r="I53" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J53" s="3"/>
-      <c r="K53" s="1" t="s">
+      <c r="J53" s="1" t="s">
         <v>452</v>
       </c>
+      <c r="K53" t="s">
+        <v>453</v>
+      </c>
       <c r="L53" t="s">
-        <v>453</v>
-      </c>
-      <c r="M53" t="s">
         <v>454</v>
       </c>
-      <c r="O53" t="s">
+      <c r="N53" t="s">
         <v>1123</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>455</v>
       </c>
@@ -6182,7 +6257,7 @@
       <c r="C54" t="s">
         <v>16</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="5">
         <v>1</v>
       </c>
       <c r="E54" t="s">
@@ -6200,21 +6275,20 @@
       <c r="I54" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J54" s="3"/>
-      <c r="K54" s="1" t="s">
+      <c r="J54" s="1" t="s">
         <v>459</v>
       </c>
+      <c r="K54" t="s">
+        <v>460</v>
+      </c>
       <c r="L54" t="s">
-        <v>460</v>
-      </c>
-      <c r="M54" t="s">
         <v>461</v>
       </c>
-      <c r="O54" t="s">
+      <c r="N54" t="s">
         <v>1124</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>462</v>
       </c>
@@ -6224,7 +6298,7 @@
       <c r="C55" t="s">
         <v>16</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="5">
         <v>1</v>
       </c>
       <c r="E55" t="s">
@@ -6242,21 +6316,20 @@
       <c r="I55" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J55" s="3"/>
-      <c r="K55" s="1" t="s">
+      <c r="J55" s="1" t="s">
         <v>468</v>
       </c>
+      <c r="K55" t="s">
+        <v>469</v>
+      </c>
       <c r="L55" t="s">
-        <v>469</v>
-      </c>
-      <c r="M55" t="s">
         <v>470</v>
       </c>
-      <c r="O55" t="s">
+      <c r="N55" t="s">
         <v>1125</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>471</v>
       </c>
@@ -6266,7 +6339,7 @@
       <c r="C56" t="s">
         <v>16</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="5">
         <v>4</v>
       </c>
       <c r="E56" t="s">
@@ -6284,21 +6357,20 @@
       <c r="I56" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J56" s="3"/>
-      <c r="K56" s="1" t="s">
+      <c r="J56" s="1" t="s">
         <v>1060</v>
       </c>
+      <c r="K56" t="s">
+        <v>477</v>
+      </c>
       <c r="L56" t="s">
-        <v>477</v>
-      </c>
-      <c r="M56" t="s">
         <v>478</v>
       </c>
-      <c r="O56" t="s">
+      <c r="N56" t="s">
         <v>1126</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>479</v>
       </c>
@@ -6308,7 +6380,7 @@
       <c r="C57" t="s">
         <v>16</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="5">
         <v>1</v>
       </c>
       <c r="E57" t="s">
@@ -6326,21 +6398,20 @@
       <c r="I57" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J57" s="3"/>
-      <c r="K57" s="1" t="s">
+      <c r="J57" s="1" t="s">
         <v>485</v>
       </c>
+      <c r="K57" t="s">
+        <v>486</v>
+      </c>
       <c r="L57" t="s">
-        <v>486</v>
-      </c>
-      <c r="M57" t="s">
         <v>487</v>
       </c>
-      <c r="O57" t="s">
+      <c r="N57" t="s">
         <v>1127</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>488</v>
       </c>
@@ -6350,7 +6421,7 @@
       <c r="C58" t="s">
         <v>16</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="5">
         <v>1</v>
       </c>
       <c r="E58" t="s">
@@ -6368,21 +6439,20 @@
       <c r="I58" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J58" s="3"/>
-      <c r="K58" s="1" t="s">
+      <c r="J58" s="1" t="s">
         <v>494</v>
       </c>
+      <c r="K58" t="s">
+        <v>495</v>
+      </c>
       <c r="L58" t="s">
-        <v>495</v>
-      </c>
-      <c r="M58" t="s">
         <v>496</v>
       </c>
-      <c r="O58" t="s">
+      <c r="N58" t="s">
         <v>1128</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>497</v>
       </c>
@@ -6392,7 +6462,7 @@
       <c r="C59" t="s">
         <v>16</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="5">
         <v>1</v>
       </c>
       <c r="E59" t="s">
@@ -6410,21 +6480,20 @@
       <c r="I59" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J59" s="3"/>
-      <c r="K59" s="1" t="s">
+      <c r="J59" s="1" t="s">
         <v>1061</v>
       </c>
+      <c r="K59" t="s">
+        <v>503</v>
+      </c>
       <c r="L59" t="s">
-        <v>503</v>
-      </c>
-      <c r="M59" t="s">
         <v>504</v>
       </c>
-      <c r="O59" t="s">
+      <c r="N59" t="s">
         <v>1129</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>505</v>
       </c>
@@ -6434,7 +6503,7 @@
       <c r="C60" t="s">
         <v>16</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="5">
         <v>3</v>
       </c>
       <c r="E60" t="s">
@@ -6452,21 +6521,20 @@
       <c r="I60" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J60" s="3"/>
-      <c r="K60" s="1" t="s">
+      <c r="J60" s="1" t="s">
         <v>1062</v>
       </c>
+      <c r="K60" t="s">
+        <v>511</v>
+      </c>
       <c r="L60" t="s">
-        <v>511</v>
-      </c>
-      <c r="M60" t="s">
         <v>512</v>
       </c>
-      <c r="O60" t="s">
+      <c r="N60" t="s">
         <v>1130</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>513</v>
       </c>
@@ -6476,7 +6544,7 @@
       <c r="C61" t="s">
         <v>16</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="5">
         <v>1</v>
       </c>
       <c r="E61" t="s">
@@ -6494,21 +6562,20 @@
       <c r="I61" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J61" s="3"/>
-      <c r="K61" s="1" t="s">
+      <c r="J61" s="1" t="s">
         <v>519</v>
       </c>
+      <c r="K61" t="s">
+        <v>520</v>
+      </c>
       <c r="L61" t="s">
-        <v>520</v>
-      </c>
-      <c r="M61" t="s">
         <v>521</v>
       </c>
-      <c r="O61" t="s">
+      <c r="N61" t="s">
         <v>1131</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>522</v>
       </c>
@@ -6518,7 +6585,7 @@
       <c r="C62" t="s">
         <v>16</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="5">
         <v>2</v>
       </c>
       <c r="E62" t="s">
@@ -6536,21 +6603,20 @@
       <c r="I62" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J62" s="3"/>
-      <c r="K62" s="1" t="s">
+      <c r="J62" s="1" t="s">
         <v>528</v>
       </c>
+      <c r="K62" t="s">
+        <v>529</v>
+      </c>
       <c r="L62" t="s">
-        <v>529</v>
-      </c>
-      <c r="M62" t="s">
         <v>530</v>
       </c>
-      <c r="O62" t="s">
+      <c r="N62" t="s">
         <v>1132</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>531</v>
       </c>
@@ -6560,7 +6626,7 @@
       <c r="C63" t="s">
         <v>16</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="5">
         <v>2</v>
       </c>
       <c r="E63" t="s">
@@ -6578,21 +6644,20 @@
       <c r="I63" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J63" s="3"/>
-      <c r="K63" s="1" t="s">
+      <c r="J63" s="1" t="s">
         <v>537</v>
       </c>
+      <c r="K63" t="s">
+        <v>538</v>
+      </c>
       <c r="L63" t="s">
-        <v>538</v>
-      </c>
-      <c r="M63" t="s">
         <v>539</v>
       </c>
-      <c r="O63" t="s">
+      <c r="N63" t="s">
         <v>1133</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="68" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>540</v>
       </c>
@@ -6602,7 +6667,7 @@
       <c r="C64" t="s">
         <v>16</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="5">
         <v>1</v>
       </c>
       <c r="E64" t="s">
@@ -6620,21 +6685,20 @@
       <c r="I64" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J64" s="3"/>
-      <c r="K64" s="1" t="s">
+      <c r="J64" s="1" t="s">
         <v>1063</v>
       </c>
+      <c r="K64" t="s">
+        <v>546</v>
+      </c>
       <c r="L64" t="s">
-        <v>546</v>
-      </c>
-      <c r="M64" t="s">
         <v>547</v>
       </c>
-      <c r="O64" t="s">
+      <c r="N64" t="s">
         <v>1134</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>548</v>
       </c>
@@ -6644,7 +6708,7 @@
       <c r="C65" t="s">
         <v>16</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="5">
         <v>2</v>
       </c>
       <c r="E65" t="s">
@@ -6662,21 +6726,20 @@
       <c r="I65" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J65" s="3"/>
-      <c r="K65" s="1" t="s">
+      <c r="J65" s="1" t="s">
         <v>554</v>
       </c>
+      <c r="K65" t="s">
+        <v>555</v>
+      </c>
       <c r="L65" t="s">
-        <v>555</v>
-      </c>
-      <c r="M65" t="s">
         <v>556</v>
       </c>
-      <c r="O65" t="s">
+      <c r="N65" t="s">
         <v>1135</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>557</v>
       </c>
@@ -6686,7 +6749,7 @@
       <c r="C66" t="s">
         <v>16</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="5">
         <v>4</v>
       </c>
       <c r="E66" t="s">
@@ -6704,21 +6767,20 @@
       <c r="I66" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J66" s="3"/>
-      <c r="K66" s="1" t="s">
+      <c r="J66" s="1" t="s">
         <v>563</v>
       </c>
+      <c r="K66" t="s">
+        <v>564</v>
+      </c>
       <c r="L66" t="s">
-        <v>564</v>
-      </c>
-      <c r="M66" t="s">
         <v>565</v>
       </c>
-      <c r="O66" t="s">
+      <c r="N66" t="s">
         <v>1136</v>
       </c>
     </row>
-    <row r="67" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>566</v>
       </c>
@@ -6728,24 +6790,24 @@
       <c r="C67" t="s">
         <v>16</v>
       </c>
+      <c r="D67" s="5"/>
       <c r="E67" t="s">
         <v>568</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J67" s="3"/>
-      <c r="K67" s="1" t="s">
+      <c r="J67" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="L67" t="s">
+      <c r="K67" t="s">
         <v>570</v>
       </c>
-      <c r="O67" t="s">
+      <c r="N67" t="s">
         <v>1137</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>571</v>
       </c>
@@ -6755,7 +6817,7 @@
       <c r="C68" t="s">
         <v>16</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="5">
         <v>2</v>
       </c>
       <c r="E68" t="s">
@@ -6773,21 +6835,20 @@
       <c r="I68" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J68" s="3"/>
-      <c r="K68" s="1" t="s">
+      <c r="J68" s="1" t="s">
         <v>577</v>
       </c>
+      <c r="K68" t="s">
+        <v>578</v>
+      </c>
       <c r="L68" t="s">
-        <v>578</v>
-      </c>
-      <c r="M68" t="s">
         <v>579</v>
       </c>
-      <c r="O68" t="s">
+      <c r="N68" t="s">
         <v>1138</v>
       </c>
     </row>
-    <row r="69" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>580</v>
       </c>
@@ -6797,7 +6858,7 @@
       <c r="C69" t="s">
         <v>16</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="5">
         <v>4</v>
       </c>
       <c r="E69" t="s">
@@ -6815,21 +6876,20 @@
       <c r="I69" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J69" s="3"/>
-      <c r="K69" s="1" t="s">
+      <c r="J69" s="1" t="s">
         <v>586</v>
       </c>
+      <c r="K69" t="s">
+        <v>587</v>
+      </c>
       <c r="L69" t="s">
-        <v>587</v>
-      </c>
-      <c r="M69" t="s">
         <v>588</v>
       </c>
-      <c r="O69" t="s">
+      <c r="N69" t="s">
         <v>1139</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>589</v>
       </c>
@@ -6839,7 +6899,7 @@
       <c r="C70" t="s">
         <v>16</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="5">
         <v>2</v>
       </c>
       <c r="E70" t="s">
@@ -6857,21 +6917,20 @@
       <c r="I70" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J70" s="3"/>
-      <c r="K70" s="1" t="s">
+      <c r="J70" s="1" t="s">
         <v>595</v>
       </c>
+      <c r="K70" t="s">
+        <v>596</v>
+      </c>
       <c r="L70" t="s">
-        <v>596</v>
-      </c>
-      <c r="M70" t="s">
         <v>597</v>
       </c>
-      <c r="O70" t="s">
+      <c r="N70" t="s">
         <v>1140</v>
       </c>
     </row>
-    <row r="71" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>598</v>
       </c>
@@ -6881,7 +6940,7 @@
       <c r="C71" t="s">
         <v>16</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="5">
         <v>4</v>
       </c>
       <c r="E71" t="s">
@@ -6899,21 +6958,20 @@
       <c r="I71" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J71" s="3"/>
-      <c r="K71" s="1" t="s">
+      <c r="J71" s="1" t="s">
         <v>604</v>
       </c>
+      <c r="K71" t="s">
+        <v>605</v>
+      </c>
       <c r="L71" t="s">
-        <v>605</v>
-      </c>
-      <c r="M71" t="s">
         <v>606</v>
       </c>
-      <c r="O71" t="s">
+      <c r="N71" t="s">
         <v>1141</v>
       </c>
     </row>
-    <row r="72" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>607</v>
       </c>
@@ -6923,6 +6981,7 @@
       <c r="C72" t="s">
         <v>16</v>
       </c>
+      <c r="D72" s="5"/>
       <c r="E72" t="s">
         <v>609</v>
       </c>
@@ -6933,18 +6992,17 @@
       <c r="I72" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J72" s="3"/>
-      <c r="K72" s="1" t="s">
+      <c r="J72" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="L72" t="s">
+      <c r="K72" t="s">
         <v>611</v>
       </c>
-      <c r="O72" t="s">
+      <c r="N72" t="s">
         <v>1142</v>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="85" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>612</v>
       </c>
@@ -6954,24 +7012,24 @@
       <c r="C73" t="s">
         <v>16</v>
       </c>
+      <c r="D73" s="5"/>
       <c r="E73" t="s">
         <v>614</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J73" s="3"/>
-      <c r="K73" s="1" t="s">
+      <c r="J73" s="1" t="s">
         <v>1064</v>
       </c>
-      <c r="L73" t="s">
+      <c r="K73" t="s">
         <v>615</v>
       </c>
-      <c r="O73" t="s">
+      <c r="N73" t="s">
         <v>1143</v>
       </c>
     </row>
-    <row r="74" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>616</v>
       </c>
@@ -6981,7 +7039,7 @@
       <c r="C74" t="s">
         <v>16</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="5">
         <v>1</v>
       </c>
       <c r="E74" t="s">
@@ -6999,21 +7057,20 @@
       <c r="I74" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J74" s="3"/>
-      <c r="K74" s="1" t="s">
+      <c r="J74" s="1" t="s">
         <v>622</v>
       </c>
+      <c r="K74" t="s">
+        <v>623</v>
+      </c>
       <c r="L74" t="s">
-        <v>623</v>
-      </c>
-      <c r="M74" t="s">
         <v>624</v>
       </c>
-      <c r="O74" t="s">
+      <c r="N74" t="s">
         <v>1144</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>625</v>
       </c>
@@ -7023,7 +7080,7 @@
       <c r="C75" t="s">
         <v>16</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="5">
         <v>2</v>
       </c>
       <c r="E75" t="s">
@@ -7041,21 +7098,20 @@
       <c r="I75" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J75" s="3"/>
-      <c r="K75" s="1" t="s">
+      <c r="J75" s="1" t="s">
         <v>631</v>
       </c>
+      <c r="K75" t="s">
+        <v>632</v>
+      </c>
       <c r="L75" t="s">
-        <v>632</v>
-      </c>
-      <c r="M75" t="s">
         <v>633</v>
       </c>
-      <c r="O75" t="s">
+      <c r="N75" t="s">
         <v>1145</v>
       </c>
     </row>
-    <row r="76" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>634</v>
       </c>
@@ -7065,7 +7121,7 @@
       <c r="C76" t="s">
         <v>16</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="5">
         <v>2</v>
       </c>
       <c r="E76" t="s">
@@ -7083,21 +7139,20 @@
       <c r="I76" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J76" s="3"/>
-      <c r="K76" s="1" t="s">
+      <c r="J76" s="1" t="s">
         <v>1065</v>
       </c>
+      <c r="K76" t="s">
+        <v>640</v>
+      </c>
       <c r="L76" t="s">
-        <v>640</v>
-      </c>
-      <c r="M76" t="s">
         <v>641</v>
       </c>
-      <c r="O76" t="s">
+      <c r="N76" t="s">
         <v>1146</v>
       </c>
     </row>
-    <row r="77" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>642</v>
       </c>
@@ -7107,7 +7162,7 @@
       <c r="C77" t="s">
         <v>16</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="5">
         <v>2</v>
       </c>
       <c r="E77" t="s">
@@ -7125,21 +7180,20 @@
       <c r="I77" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J77" s="3"/>
-      <c r="K77" s="1" t="s">
+      <c r="J77" s="1" t="s">
         <v>647</v>
       </c>
+      <c r="K77" t="s">
+        <v>648</v>
+      </c>
       <c r="L77" t="s">
-        <v>648</v>
-      </c>
-      <c r="M77" t="s">
         <v>649</v>
       </c>
-      <c r="O77" t="s">
+      <c r="N77" t="s">
         <v>1147</v>
       </c>
     </row>
-    <row r="78" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>650</v>
       </c>
@@ -7149,7 +7203,7 @@
       <c r="C78" t="s">
         <v>16</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="5">
         <v>1</v>
       </c>
       <c r="E78" t="s">
@@ -7167,21 +7221,20 @@
       <c r="I78" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J78" s="3"/>
-      <c r="K78" s="1" t="s">
+      <c r="J78" s="1" t="s">
         <v>655</v>
       </c>
+      <c r="K78" t="s">
+        <v>656</v>
+      </c>
       <c r="L78" t="s">
-        <v>656</v>
-      </c>
-      <c r="M78" t="s">
         <v>657</v>
       </c>
-      <c r="O78" t="s">
+      <c r="N78" t="s">
         <v>1148</v>
       </c>
     </row>
-    <row r="79" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>658</v>
       </c>
@@ -7191,7 +7244,7 @@
       <c r="C79" t="s">
         <v>16</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="5">
         <v>3</v>
       </c>
       <c r="E79" t="s">
@@ -7209,21 +7262,20 @@
       <c r="I79" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J79" s="3"/>
-      <c r="K79" s="1" t="s">
+      <c r="J79" s="1" t="s">
         <v>663</v>
       </c>
+      <c r="K79" t="s">
+        <v>664</v>
+      </c>
       <c r="L79" t="s">
-        <v>664</v>
-      </c>
-      <c r="M79" t="s">
         <v>665</v>
       </c>
-      <c r="O79" t="s">
+      <c r="N79" t="s">
         <v>1149</v>
       </c>
     </row>
-    <row r="80" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>666</v>
       </c>
@@ -7233,7 +7285,7 @@
       <c r="C80" t="s">
         <v>16</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="5">
         <v>4</v>
       </c>
       <c r="E80" t="s">
@@ -7251,18 +7303,17 @@
       <c r="I80" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J80" s="3"/>
-      <c r="K80" s="1" t="s">
+      <c r="J80" s="1" t="s">
         <v>1066</v>
       </c>
-      <c r="L80" t="s">
+      <c r="K80" t="s">
         <v>671</v>
       </c>
-      <c r="O80" t="s">
+      <c r="N80" t="s">
         <v>1150</v>
       </c>
     </row>
-    <row r="81" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:15" ht="68" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>672</v>
       </c>
@@ -7272,24 +7323,24 @@
       <c r="C81" t="s">
         <v>16</v>
       </c>
+      <c r="D81" s="5"/>
       <c r="E81" t="s">
         <v>674</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J81" s="3"/>
-      <c r="K81" s="1" t="s">
+      <c r="J81" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="L81" t="s">
+      <c r="K81" t="s">
         <v>676</v>
       </c>
-      <c r="O81" t="s">
+      <c r="N81" t="s">
         <v>1151</v>
       </c>
     </row>
-    <row r="82" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:15" ht="68" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>677</v>
       </c>
@@ -7299,24 +7350,24 @@
       <c r="C82" t="s">
         <v>16</v>
       </c>
+      <c r="D82" s="5"/>
       <c r="E82" t="s">
         <v>679</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J82" s="3"/>
-      <c r="K82" s="1" t="s">
+      <c r="J82" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="L82" t="s">
+      <c r="K82" t="s">
         <v>681</v>
       </c>
-      <c r="O82" t="s">
+      <c r="N82" t="s">
         <v>1152</v>
       </c>
     </row>
-    <row r="83" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>682</v>
       </c>
@@ -7326,7 +7377,7 @@
       <c r="C83" t="s">
         <v>16</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="5">
         <v>4</v>
       </c>
       <c r="E83" t="s">
@@ -7344,21 +7395,20 @@
       <c r="I83" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J83" s="3"/>
-      <c r="K83" s="1" t="s">
+      <c r="J83" s="1" t="s">
         <v>688</v>
       </c>
+      <c r="K83" t="s">
+        <v>689</v>
+      </c>
       <c r="L83" t="s">
-        <v>689</v>
-      </c>
-      <c r="M83" t="s">
         <v>690</v>
       </c>
-      <c r="O83" t="s">
+      <c r="N83" t="s">
         <v>1153</v>
       </c>
     </row>
-    <row r="84" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:15" ht="85" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>691</v>
       </c>
@@ -7368,7 +7418,7 @@
       <c r="C84" t="s">
         <v>16</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="5">
         <v>1</v>
       </c>
       <c r="E84" t="s">
@@ -7386,21 +7436,20 @@
       <c r="I84" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J84" s="3"/>
-      <c r="K84" s="1" t="s">
+      <c r="J84" s="1" t="s">
         <v>1067</v>
       </c>
+      <c r="K84" t="s">
+        <v>697</v>
+      </c>
       <c r="L84" t="s">
-        <v>697</v>
-      </c>
-      <c r="M84" t="s">
         <v>698</v>
       </c>
-      <c r="O84" t="s">
+      <c r="N84" t="s">
         <v>1154</v>
       </c>
     </row>
-    <row r="85" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>699</v>
       </c>
@@ -7410,7 +7459,7 @@
       <c r="C85" t="s">
         <v>16</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="5">
         <v>3</v>
       </c>
       <c r="E85" t="s">
@@ -7428,21 +7477,20 @@
       <c r="I85" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J85" s="3"/>
-      <c r="K85" s="1" t="s">
+      <c r="J85" s="1" t="s">
         <v>1070</v>
       </c>
+      <c r="K85" t="s">
+        <v>705</v>
+      </c>
       <c r="L85" t="s">
-        <v>705</v>
-      </c>
-      <c r="M85" t="s">
         <v>706</v>
       </c>
-      <c r="O85" t="s">
+      <c r="N85" t="s">
         <v>1155</v>
       </c>
     </row>
-    <row r="86" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:15" ht="68" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>707</v>
       </c>
@@ -7452,7 +7500,7 @@
       <c r="C86" t="s">
         <v>16</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="5">
         <v>2</v>
       </c>
       <c r="E86" t="s">
@@ -7470,21 +7518,20 @@
       <c r="I86" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J86" s="3"/>
-      <c r="K86" s="1" t="s">
+      <c r="J86" s="1" t="s">
         <v>1068</v>
       </c>
+      <c r="K86" t="s">
+        <v>713</v>
+      </c>
       <c r="L86" t="s">
-        <v>713</v>
-      </c>
-      <c r="M86" t="s">
         <v>714</v>
       </c>
-      <c r="O86" t="s">
+      <c r="N86" t="s">
         <v>1156</v>
       </c>
     </row>
-    <row r="87" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:15" ht="85" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>715</v>
       </c>
@@ -7494,7 +7541,7 @@
       <c r="C87" t="s">
         <v>16</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="5">
         <v>2</v>
       </c>
       <c r="E87" t="s">
@@ -7512,21 +7559,20 @@
       <c r="I87" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J87" s="3"/>
-      <c r="K87" s="1" t="s">
+      <c r="J87" s="1" t="s">
         <v>1069</v>
       </c>
+      <c r="K87" t="s">
+        <v>721</v>
+      </c>
       <c r="L87" t="s">
-        <v>721</v>
-      </c>
-      <c r="M87" t="s">
         <v>722</v>
       </c>
-      <c r="O87" t="s">
+      <c r="N87" t="s">
         <v>1157</v>
       </c>
     </row>
-    <row r="88" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:15" ht="119" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>723</v>
       </c>
@@ -7536,24 +7582,24 @@
       <c r="C88" t="s">
         <v>16</v>
       </c>
+      <c r="D88" s="5"/>
       <c r="E88" t="s">
         <v>725</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J88" s="3"/>
-      <c r="K88" s="1" t="s">
+      <c r="J88" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="L88" t="s">
+      <c r="K88" t="s">
         <v>727</v>
       </c>
-      <c r="O88" t="s">
+      <c r="N88" t="s">
         <v>1158</v>
       </c>
     </row>
-    <row r="89" spans="1:16" ht="68" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:15" ht="136" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>728</v>
       </c>
@@ -7563,7 +7609,7 @@
       <c r="C89" t="s">
         <v>16</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="5">
         <v>1</v>
       </c>
       <c r="E89" t="s">
@@ -7581,21 +7627,20 @@
       <c r="I89" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J89" s="3"/>
-      <c r="K89" s="1" t="s">
+      <c r="J89" s="1" t="s">
         <v>734</v>
       </c>
+      <c r="K89" t="s">
+        <v>735</v>
+      </c>
       <c r="L89" t="s">
-        <v>735</v>
-      </c>
-      <c r="M89" t="s">
         <v>736</v>
       </c>
-      <c r="O89" t="s">
+      <c r="N89" t="s">
         <v>1159</v>
       </c>
     </row>
-    <row r="90" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:15" ht="85" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>737</v>
       </c>
@@ -7605,7 +7650,7 @@
       <c r="C90" t="s">
         <v>16</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="5">
         <v>7</v>
       </c>
       <c r="E90" t="s">
@@ -7623,21 +7668,20 @@
       <c r="I90" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J90" s="3"/>
-      <c r="K90" s="1" t="s">
+      <c r="J90" s="1" t="s">
         <v>743</v>
       </c>
+      <c r="K90" t="s">
+        <v>744</v>
+      </c>
       <c r="L90" t="s">
-        <v>744</v>
-      </c>
-      <c r="M90" t="s">
         <v>745</v>
       </c>
-      <c r="O90" t="s">
+      <c r="N90" t="s">
         <v>1170</v>
       </c>
     </row>
-    <row r="91" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:15" ht="68" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>746</v>
       </c>
@@ -7647,7 +7691,7 @@
       <c r="C91" t="s">
         <v>16</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="5">
         <v>2</v>
       </c>
       <c r="E91" t="s">
@@ -7665,21 +7709,20 @@
       <c r="I91" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J91" s="3"/>
-      <c r="K91" s="1" t="s">
+      <c r="J91" s="1" t="s">
         <v>752</v>
       </c>
+      <c r="K91" t="s">
+        <v>753</v>
+      </c>
       <c r="L91" t="s">
-        <v>753</v>
-      </c>
-      <c r="M91" t="s">
         <v>754</v>
       </c>
-      <c r="O91" t="s">
+      <c r="N91" t="s">
         <v>1160</v>
       </c>
     </row>
-    <row r="92" spans="1:16" ht="102" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:15" ht="170" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>755</v>
       </c>
@@ -7689,7 +7732,7 @@
       <c r="C92" t="s">
         <v>16</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="5">
         <v>2</v>
       </c>
       <c r="E92" t="s">
@@ -7707,24 +7750,23 @@
       <c r="I92" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J92" s="3"/>
-      <c r="K92" s="1" t="s">
+      <c r="J92" s="1" t="s">
         <v>1071</v>
       </c>
+      <c r="K92" t="s">
+        <v>761</v>
+      </c>
       <c r="L92" t="s">
-        <v>761</v>
-      </c>
-      <c r="M92" t="s">
         <v>762</v>
       </c>
-      <c r="O92" t="s">
+      <c r="N92" t="s">
         <v>1161</v>
       </c>
-      <c r="P92">
+      <c r="O92">
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>763</v>
       </c>
@@ -7734,7 +7776,7 @@
       <c r="C93" t="s">
         <v>16</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="5">
         <v>7</v>
       </c>
       <c r="E93" t="s">
@@ -7752,21 +7794,20 @@
       <c r="I93" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J93" s="3"/>
-      <c r="K93" s="1" t="s">
+      <c r="J93" s="1" t="s">
         <v>769</v>
       </c>
+      <c r="K93" t="s">
+        <v>770</v>
+      </c>
       <c r="L93" t="s">
-        <v>770</v>
-      </c>
-      <c r="M93" t="s">
         <v>771</v>
       </c>
-      <c r="O93" t="s">
+      <c r="N93" t="s">
         <v>1162</v>
       </c>
     </row>
-    <row r="94" spans="1:16" ht="34" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>772</v>
       </c>
@@ -7776,7 +7817,7 @@
       <c r="C94" t="s">
         <v>16</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="5">
         <v>2</v>
       </c>
       <c r="E94" t="s">
@@ -7794,21 +7835,20 @@
       <c r="I94" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J94" s="3"/>
-      <c r="K94" s="1" t="s">
+      <c r="J94" s="1" t="s">
         <v>778</v>
       </c>
+      <c r="K94" t="s">
+        <v>779</v>
+      </c>
       <c r="L94" t="s">
-        <v>779</v>
-      </c>
-      <c r="M94" t="s">
         <v>780</v>
       </c>
-      <c r="O94" t="s">
+      <c r="N94" t="s">
         <v>1163</v>
       </c>
     </row>
-    <row r="95" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>781</v>
       </c>
@@ -7818,7 +7858,7 @@
       <c r="C95" t="s">
         <v>16</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="5">
         <v>2</v>
       </c>
       <c r="E95" t="s">
@@ -7836,21 +7876,20 @@
       <c r="I95" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J95" s="3"/>
-      <c r="K95" s="1" t="s">
+      <c r="J95" s="1" t="s">
         <v>1072</v>
       </c>
+      <c r="K95" t="s">
+        <v>787</v>
+      </c>
       <c r="L95" t="s">
-        <v>787</v>
-      </c>
-      <c r="M95" t="s">
         <v>788</v>
       </c>
-      <c r="O95" t="s">
+      <c r="N95" t="s">
         <v>1164</v>
       </c>
     </row>
-    <row r="96" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>789</v>
       </c>
@@ -7860,7 +7899,7 @@
       <c r="C96" t="s">
         <v>16</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="5">
         <v>7</v>
       </c>
       <c r="E96" t="s">
@@ -7878,21 +7917,20 @@
       <c r="I96" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J96" s="3"/>
-      <c r="K96" s="1" t="s">
+      <c r="J96" s="1" t="s">
         <v>795</v>
       </c>
+      <c r="K96" t="s">
+        <v>796</v>
+      </c>
       <c r="L96" t="s">
-        <v>796</v>
-      </c>
-      <c r="M96" t="s">
         <v>797</v>
       </c>
-      <c r="O96" t="s">
+      <c r="N96" t="s">
         <v>1165</v>
       </c>
     </row>
-    <row r="97" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>798</v>
       </c>
@@ -7902,7 +7940,7 @@
       <c r="C97" t="s">
         <v>16</v>
       </c>
-      <c r="D97">
+      <c r="D97" s="5">
         <v>1</v>
       </c>
       <c r="E97" t="s">
@@ -7920,21 +7958,20 @@
       <c r="I97" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J97" s="3"/>
-      <c r="K97" s="1" t="s">
+      <c r="J97" s="1" t="s">
         <v>804</v>
       </c>
+      <c r="K97" t="s">
+        <v>805</v>
+      </c>
       <c r="L97" t="s">
-        <v>805</v>
-      </c>
-      <c r="M97" t="s">
         <v>806</v>
       </c>
-      <c r="O97" t="s">
+      <c r="N97" t="s">
         <v>1166</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>807</v>
       </c>
@@ -7944,18 +7981,19 @@
       <c r="C98" t="s">
         <v>16</v>
       </c>
+      <c r="D98" s="5"/>
       <c r="E98" t="s">
         <v>809</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J98" s="3"/>
-      <c r="L98" t="s">
+      <c r="J98" s="1"/>
+      <c r="K98" t="s">
         <v>810</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>811</v>
       </c>
@@ -7965,18 +8003,19 @@
       <c r="C99" t="s">
         <v>16</v>
       </c>
+      <c r="D99" s="5"/>
       <c r="E99" t="s">
         <v>813</v>
       </c>
       <c r="I99" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J99" s="3"/>
-      <c r="L99" t="s">
+      <c r="J99" s="1"/>
+      <c r="K99" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>815</v>
       </c>
@@ -7986,7 +8025,7 @@
       <c r="C100" t="s">
         <v>16</v>
       </c>
-      <c r="D100">
+      <c r="D100" s="5">
         <v>1</v>
       </c>
       <c r="E100" t="s">
@@ -8004,15 +8043,15 @@
       <c r="I100" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J100" s="3"/>
+      <c r="J100" s="1"/>
+      <c r="K100" t="s">
+        <v>821</v>
+      </c>
       <c r="L100" t="s">
-        <v>821</v>
-      </c>
-      <c r="M100" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>823</v>
       </c>
@@ -8022,18 +8061,19 @@
       <c r="C101" t="s">
         <v>16</v>
       </c>
+      <c r="D101" s="5"/>
       <c r="E101" t="s">
         <v>825</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J101" s="3"/>
-      <c r="L101" t="s">
+      <c r="J101" s="1"/>
+      <c r="K101" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>827</v>
       </c>
@@ -8043,7 +8083,7 @@
       <c r="C102" t="s">
         <v>16</v>
       </c>
-      <c r="D102">
+      <c r="D102" s="5">
         <v>2</v>
       </c>
       <c r="E102" t="s">
@@ -8061,15 +8101,15 @@
       <c r="I102" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J102" s="3"/>
+      <c r="J102" s="1"/>
+      <c r="K102" t="s">
+        <v>831</v>
+      </c>
       <c r="L102" t="s">
-        <v>831</v>
-      </c>
-      <c r="M102" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="103" spans="1:15" ht="51" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>833</v>
       </c>
@@ -8079,7 +8119,7 @@
       <c r="C103" t="s">
         <v>16</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="5">
         <v>4</v>
       </c>
       <c r="E103" t="s">
@@ -8097,15 +8137,15 @@
       <c r="I103" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J103" s="3"/>
-      <c r="K103" s="1" t="s">
+      <c r="J103" s="1" t="s">
         <v>839</v>
       </c>
-      <c r="O103" t="s">
+      <c r="K103"/>
+      <c r="N103" t="s">
         <v>1167</v>
       </c>
     </row>
-    <row r="104" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:14" ht="68" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>840</v>
       </c>
@@ -8115,7 +8155,7 @@
       <c r="C104" t="s">
         <v>16</v>
       </c>
-      <c r="D104">
+      <c r="D104" s="5">
         <v>1</v>
       </c>
       <c r="E104" t="s">
@@ -8133,15 +8173,15 @@
       <c r="I104" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J104" s="3"/>
-      <c r="K104" s="1" t="s">
+      <c r="J104" s="1" t="s">
         <v>845</v>
       </c>
-      <c r="O104" t="s">
+      <c r="K104"/>
+      <c r="N104" t="s">
         <v>1168</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>846</v>
       </c>
@@ -8151,15 +8191,17 @@
       <c r="C105" t="s">
         <v>16</v>
       </c>
+      <c r="D105" s="5"/>
       <c r="E105" t="s">
         <v>848</v>
       </c>
       <c r="I105" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J105" s="3"/>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="J105" s="1"/>
+      <c r="K105"/>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>849</v>
       </c>
@@ -8169,7 +8211,7 @@
       <c r="C106" t="s">
         <v>16</v>
       </c>
-      <c r="D106">
+      <c r="D106" s="5">
         <v>1</v>
       </c>
       <c r="E106" t="s">
@@ -8187,9 +8229,10 @@
       <c r="I106" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J106" s="3"/>
-    </row>
-    <row r="107" spans="1:15" ht="34" x14ac:dyDescent="0.2">
+      <c r="J106" s="1"/>
+      <c r="K106"/>
+    </row>
+    <row r="107" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>856</v>
       </c>
@@ -8199,7 +8242,7 @@
       <c r="C107" t="s">
         <v>16</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="5">
         <v>4</v>
       </c>
       <c r="E107" t="s">
@@ -8217,15 +8260,15 @@
       <c r="I107" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J107" s="3"/>
-      <c r="K107" s="2" t="s">
+      <c r="J107" s="2" t="s">
         <v>862</v>
       </c>
-      <c r="O107" t="s">
+      <c r="K107"/>
+      <c r="N107" t="s">
         <v>1169</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>863</v>
       </c>
@@ -8235,7 +8278,7 @@
       <c r="C108" t="s">
         <v>16</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="5">
         <v>7</v>
       </c>
       <c r="E108" t="s">
@@ -8253,9 +8296,10 @@
       <c r="I108" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J108" s="3"/>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="J108" s="1"/>
+      <c r="K108"/>
+    </row>
+    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>869</v>
       </c>
@@ -8265,7 +8309,7 @@
       <c r="C109" t="s">
         <v>16</v>
       </c>
-      <c r="D109">
+      <c r="D109" s="5">
         <v>4</v>
       </c>
       <c r="E109" t="s">
@@ -8283,9 +8327,10 @@
       <c r="I109" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J109" s="3"/>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="J109" s="1"/>
+      <c r="K109"/>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>875</v>
       </c>
@@ -8295,7 +8340,7 @@
       <c r="C110" t="s">
         <v>16</v>
       </c>
-      <c r="D110">
+      <c r="D110" s="5">
         <v>7</v>
       </c>
       <c r="E110" t="s">
@@ -8313,9 +8358,10 @@
       <c r="I110" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J110" s="3"/>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="J110" s="1"/>
+      <c r="K110"/>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>881</v>
       </c>
@@ -8325,7 +8371,7 @@
       <c r="C111" t="s">
         <v>16</v>
       </c>
-      <c r="D111">
+      <c r="D111" s="5">
         <v>7</v>
       </c>
       <c r="E111" t="s">
@@ -8343,9 +8389,10 @@
       <c r="I111" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J111" s="3"/>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="J111" s="1"/>
+      <c r="K111"/>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>887</v>
       </c>
@@ -8355,7 +8402,7 @@
       <c r="C112" t="s">
         <v>16</v>
       </c>
-      <c r="D112">
+      <c r="D112" s="5">
         <v>7</v>
       </c>
       <c r="E112" t="s">
@@ -8373,9 +8420,10 @@
       <c r="I112" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J112" s="3"/>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J112" s="1"/>
+      <c r="K112"/>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>893</v>
       </c>
@@ -8385,7 +8433,7 @@
       <c r="C113" t="s">
         <v>16</v>
       </c>
-      <c r="D113">
+      <c r="D113" s="5">
         <v>7</v>
       </c>
       <c r="E113" t="s">
@@ -8401,13 +8449,12 @@
         <v>898</v>
       </c>
       <c r="I113" t="s">
-        <v>1173</v>
-      </c>
-      <c r="J113" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1171</v>
+      </c>
+      <c r="J113" s="1"/>
+      <c r="K113"/>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>899</v>
       </c>
@@ -8417,7 +8464,7 @@
       <c r="C114" t="s">
         <v>16</v>
       </c>
-      <c r="D114">
+      <c r="D114" s="5">
         <v>7</v>
       </c>
       <c r="E114" t="s">
@@ -8435,9 +8482,10 @@
       <c r="I114" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J114" s="3"/>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J114" s="1"/>
+      <c r="K114"/>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>905</v>
       </c>
@@ -8447,7 +8495,7 @@
       <c r="C115" t="s">
         <v>16</v>
       </c>
-      <c r="D115">
+      <c r="D115" s="5">
         <v>2</v>
       </c>
       <c r="E115" t="s">
@@ -8465,9 +8513,10 @@
       <c r="I115" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J115" s="3"/>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J115" s="1"/>
+      <c r="K115"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>911</v>
       </c>
@@ -8477,7 +8526,7 @@
       <c r="C116" t="s">
         <v>16</v>
       </c>
-      <c r="D116">
+      <c r="D116" s="5">
         <v>7</v>
       </c>
       <c r="E116" t="s">
@@ -8495,9 +8544,10 @@
       <c r="I116" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J116" s="3"/>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J116" s="1"/>
+      <c r="K116"/>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>917</v>
       </c>
@@ -8507,7 +8557,7 @@
       <c r="C117" t="s">
         <v>16</v>
       </c>
-      <c r="D117">
+      <c r="D117" s="5">
         <v>7</v>
       </c>
       <c r="E117" t="s">
@@ -8525,9 +8575,10 @@
       <c r="I117" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J117" s="3"/>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J117" s="1"/>
+      <c r="K117"/>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>923</v>
       </c>
@@ -8537,7 +8588,7 @@
       <c r="C118" t="s">
         <v>16</v>
       </c>
-      <c r="D118">
+      <c r="D118" s="5">
         <v>7</v>
       </c>
       <c r="E118" t="s">
@@ -8553,13 +8604,12 @@
         <v>928</v>
       </c>
       <c r="I118" t="s">
-        <v>1173</v>
-      </c>
-      <c r="J118" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1171</v>
+      </c>
+      <c r="J118" s="1"/>
+      <c r="K118"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>929</v>
       </c>
@@ -8569,7 +8619,7 @@
       <c r="C119" t="s">
         <v>16</v>
       </c>
-      <c r="D119">
+      <c r="D119" s="5">
         <v>7</v>
       </c>
       <c r="E119" t="s">
@@ -8585,13 +8635,12 @@
         <v>934</v>
       </c>
       <c r="I119" t="s">
-        <v>1173</v>
-      </c>
-      <c r="J119" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1171</v>
+      </c>
+      <c r="J119" s="1"/>
+      <c r="K119"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>935</v>
       </c>
@@ -8601,7 +8650,7 @@
       <c r="C120" t="s">
         <v>16</v>
       </c>
-      <c r="D120">
+      <c r="D120" s="5">
         <v>1</v>
       </c>
       <c r="E120" t="s">
@@ -8619,9 +8668,10 @@
       <c r="I120" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J120" s="3"/>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J120" s="1"/>
+      <c r="K120"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>941</v>
       </c>
@@ -8631,7 +8681,7 @@
       <c r="C121" t="s">
         <v>16</v>
       </c>
-      <c r="D121">
+      <c r="D121" s="5">
         <v>7</v>
       </c>
       <c r="E121" t="s">
@@ -8647,13 +8697,12 @@
         <v>946</v>
       </c>
       <c r="I121" t="s">
-        <v>1173</v>
-      </c>
-      <c r="J121" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1171</v>
+      </c>
+      <c r="J121" s="1"/>
+      <c r="K121"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>947</v>
       </c>
@@ -8663,7 +8712,7 @@
       <c r="C122" t="s">
         <v>16</v>
       </c>
-      <c r="D122">
+      <c r="D122" s="5">
         <v>7</v>
       </c>
       <c r="E122" t="s">
@@ -8681,8 +8730,10 @@
       <c r="I122" t="s">
         <v>1041</v>
       </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J122" s="1"/>
+      <c r="K122"/>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>953</v>
       </c>
@@ -8692,7 +8743,7 @@
       <c r="C123" t="s">
         <v>16</v>
       </c>
-      <c r="D123">
+      <c r="D123" s="5">
         <v>2</v>
       </c>
       <c r="E123" t="s">
@@ -8710,9 +8761,10 @@
       <c r="I123" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J123" s="3"/>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J123" s="1"/>
+      <c r="K123"/>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>959</v>
       </c>
@@ -8722,7 +8774,7 @@
       <c r="C124" t="s">
         <v>16</v>
       </c>
-      <c r="D124">
+      <c r="D124" s="5">
         <v>1</v>
       </c>
       <c r="E124" t="s">
@@ -8740,9 +8792,10 @@
       <c r="I124" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J124" s="3"/>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J124" s="1"/>
+      <c r="K124"/>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>965</v>
       </c>
@@ -8752,7 +8805,7 @@
       <c r="C125" t="s">
         <v>16</v>
       </c>
-      <c r="D125">
+      <c r="D125" s="5">
         <v>7</v>
       </c>
       <c r="E125" t="s">
@@ -8770,9 +8823,10 @@
       <c r="I125" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J125" s="3"/>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J125" s="1"/>
+      <c r="K125"/>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>971</v>
       </c>
@@ -8782,7 +8836,7 @@
       <c r="C126" t="s">
         <v>16</v>
       </c>
-      <c r="D126">
+      <c r="D126" s="5">
         <v>1</v>
       </c>
       <c r="E126" t="s">
@@ -8800,9 +8854,10 @@
       <c r="I126" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J126" s="3"/>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J126" s="1"/>
+      <c r="K126"/>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>977</v>
       </c>
@@ -8812,7 +8867,7 @@
       <c r="C127" t="s">
         <v>16</v>
       </c>
-      <c r="D127">
+      <c r="D127" s="5">
         <v>7</v>
       </c>
       <c r="E127" s="3" t="s">
@@ -8830,9 +8885,10 @@
       <c r="I127" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J127" s="3"/>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J127" s="1"/>
+      <c r="K127"/>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>983</v>
       </c>
@@ -8842,7 +8898,7 @@
       <c r="C128" t="s">
         <v>16</v>
       </c>
-      <c r="D128">
+      <c r="D128" s="5">
         <v>2</v>
       </c>
       <c r="E128" s="3" t="s">
@@ -8860,9 +8916,10 @@
       <c r="I128" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J128" s="3"/>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J128" s="1"/>
+      <c r="K128"/>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>989</v>
       </c>
@@ -8872,7 +8929,7 @@
       <c r="C129" t="s">
         <v>16</v>
       </c>
-      <c r="D129">
+      <c r="D129" s="5">
         <v>1</v>
       </c>
       <c r="E129" s="3" t="s">
@@ -8890,9 +8947,10 @@
       <c r="I129" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J129" s="3"/>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J129" s="1"/>
+      <c r="K129"/>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>995</v>
       </c>
@@ -8902,7 +8960,7 @@
       <c r="C130" t="s">
         <v>16</v>
       </c>
-      <c r="D130">
+      <c r="D130" s="5">
         <v>2</v>
       </c>
       <c r="E130" s="3" t="s">
@@ -8920,9 +8978,10 @@
       <c r="I130" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J130" s="3"/>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J130" s="1"/>
+      <c r="K130"/>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>1001</v>
       </c>
@@ -8932,7 +8991,7 @@
       <c r="C131" t="s">
         <v>16</v>
       </c>
-      <c r="D131">
+      <c r="D131" s="5">
         <v>3</v>
       </c>
       <c r="E131" s="3" t="s">
@@ -8950,9 +9009,10 @@
       <c r="I131" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J131" s="3"/>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J131" s="1"/>
+      <c r="K131"/>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>1007</v>
       </c>
@@ -8962,7 +9022,7 @@
       <c r="C132" t="s">
         <v>16</v>
       </c>
-      <c r="D132">
+      <c r="D132" s="5">
         <v>4</v>
       </c>
       <c r="E132" s="3" t="s">
@@ -8980,9 +9040,10 @@
       <c r="I132" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J132" s="3"/>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J132" s="1"/>
+      <c r="K132"/>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>1013</v>
       </c>
@@ -8992,7 +9053,7 @@
       <c r="C133" t="s">
         <v>16</v>
       </c>
-      <c r="D133">
+      <c r="D133" s="5">
         <v>1</v>
       </c>
       <c r="E133" s="3" t="s">
@@ -9010,9 +9071,10 @@
       <c r="I133" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J133" s="3"/>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J133" s="1"/>
+      <c r="K133"/>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>1019</v>
       </c>
@@ -9022,7 +9084,7 @@
       <c r="C134" t="s">
         <v>16</v>
       </c>
-      <c r="D134">
+      <c r="D134" s="5">
         <v>1</v>
       </c>
       <c r="E134" s="3" t="s">
@@ -9040,9 +9102,10 @@
       <c r="I134" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J134" s="3"/>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J134" s="1"/>
+      <c r="K134"/>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>1025</v>
       </c>
@@ -9052,7 +9115,7 @@
       <c r="C135" t="s">
         <v>16</v>
       </c>
-      <c r="D135">
+      <c r="D135" s="5">
         <v>1</v>
       </c>
       <c r="E135" s="3" t="s">
@@ -9070,9 +9133,10 @@
       <c r="I135" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J135" s="3"/>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J135" s="1"/>
+      <c r="K135"/>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>1035</v>
       </c>
@@ -9082,7 +9146,7 @@
       <c r="C136" t="s">
         <v>16</v>
       </c>
-      <c r="D136">
+      <c r="D136" s="5">
         <v>1</v>
       </c>
       <c r="E136" s="3" t="s">
@@ -9100,9 +9164,10 @@
       <c r="I136" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J136" s="3"/>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J136" s="1"/>
+      <c r="K136"/>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>24</v>
       </c>
@@ -9112,7 +9177,7 @@
       <c r="C137" t="s">
         <v>16</v>
       </c>
-      <c r="D137">
+      <c r="D137" s="5">
         <v>1</v>
       </c>
       <c r="E137" s="3" t="s">
@@ -9128,13 +9193,12 @@
         <v>29</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>1175</v>
-      </c>
-      <c r="J137" s="3" t="s">
-        <v>1176</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
+        <v>1173</v>
+      </c>
+      <c r="J137" s="1"/>
+      <c r="K137"/>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>1046</v>
       </c>
@@ -9144,7 +9208,7 @@
       <c r="C138" t="s">
         <v>16</v>
       </c>
-      <c r="D138">
+      <c r="D138" s="5">
         <v>4</v>
       </c>
       <c r="E138" s="3" t="s">
@@ -9162,9 +9226,10 @@
       <c r="I138" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J138" s="3"/>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J138" s="1"/>
+      <c r="K138"/>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>1050</v>
       </c>
@@ -9174,7 +9239,7 @@
       <c r="C139" t="s">
         <v>16</v>
       </c>
-      <c r="D139">
+      <c r="D139" s="5">
         <v>2</v>
       </c>
       <c r="E139" s="3" t="s">
@@ -9192,7 +9257,225 @@
       <c r="I139" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="J139" s="3"/>
+      <c r="J139" s="1"/>
+      <c r="K139"/>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B140" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C140" t="s">
+        <v>16</v>
+      </c>
+      <c r="D140" s="5">
+        <v>2</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>1176</v>
+      </c>
+      <c r="F140" t="s">
+        <v>1177</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>1178</v>
+      </c>
+      <c r="H140" t="s">
+        <v>1179</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="J140" s="1"/>
+      <c r="K140"/>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C141" t="s">
+        <v>16</v>
+      </c>
+      <c r="D141" s="5">
+        <v>2</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F141" t="s">
+        <v>1183</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>1184</v>
+      </c>
+      <c r="H141" t="s">
+        <v>1185</v>
+      </c>
+      <c r="I141" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="J141" s="1"/>
+      <c r="K141"/>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B142" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C142" t="s">
+        <v>16</v>
+      </c>
+      <c r="D142" s="5">
+        <v>2</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>1188</v>
+      </c>
+      <c r="F142" t="s">
+        <v>1189</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>1190</v>
+      </c>
+      <c r="H142" t="s">
+        <v>1191</v>
+      </c>
+      <c r="I142" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="J142" s="1"/>
+      <c r="K142"/>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B143" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C143" t="s">
+        <v>16</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F143" t="s">
+        <v>1196</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H143" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I143" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="J143" s="1"/>
+      <c r="K143"/>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B144" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C144" t="s">
+        <v>16</v>
+      </c>
+      <c r="D144" s="5">
+        <v>1</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F144" t="s">
+        <v>1202</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>1203</v>
+      </c>
+      <c r="H144" t="s">
+        <v>1204</v>
+      </c>
+      <c r="I144" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="J144" s="1"/>
+      <c r="K144"/>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B145" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C145" t="s">
+        <v>16</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>1207</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="F145" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="H145" t="s">
+        <v>1211</v>
+      </c>
+      <c r="I145" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="J145" s="1"/>
+      <c r="K145"/>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C146" t="s">
+        <v>16</v>
+      </c>
+      <c r="D146" s="5" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>1215</v>
+      </c>
+      <c r="F146" t="s">
+        <v>1216</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>1217</v>
+      </c>
+      <c r="H146" t="s">
+        <v>1218</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="J146" s="1"/>
+      <c r="K146"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
